--- a/grc_wisdom_api/scripts/verify/_tmp/Framework_coverage.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp/Framework_coverage.xlsx
@@ -36,7 +36,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -48,7 +48,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1172-20260923105942</t>
+    <t>97EF-20260924223621</t>
   </si>
   <si>
     <t>Standard</t>
